--- a/artfynd/A 35174-2026 artfynd.xlsx
+++ b/artfynd/A 35174-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136370044</v>
       </c>
       <c r="B2" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>136418477</v>
       </c>
       <c r="B3" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>136418555</v>
       </c>
       <c r="B4" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>136370107</v>
       </c>
       <c r="B27" t="n">
-        <v>106358</v>
+        <v>106361</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 35174-2026 artfynd.xlsx
+++ b/artfynd/A 35174-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136370044</v>
       </c>
       <c r="B2" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>136418477</v>
       </c>
       <c r="B3" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>136418555</v>
       </c>
       <c r="B4" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>136370107</v>
       </c>
       <c r="B27" t="n">
-        <v>106361</v>
+        <v>106362</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 35174-2026 artfynd.xlsx
+++ b/artfynd/A 35174-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136370044</v>
       </c>
       <c r="B2" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>136418477</v>
       </c>
       <c r="B3" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>136418555</v>
       </c>
       <c r="B4" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136370093</v>
       </c>
       <c r="B5" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>136390346</v>
       </c>
       <c r="B6" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>136390391</v>
       </c>
       <c r="B7" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>136390547</v>
       </c>
       <c r="B8" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>136390574</v>
       </c>
       <c r="B9" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>136390613</v>
       </c>
       <c r="B10" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>136390682</v>
       </c>
       <c r="B11" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>136391062</v>
       </c>
       <c r="B12" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>136391089</v>
       </c>
       <c r="B13" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>136391098</v>
       </c>
       <c r="B14" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>136391109</v>
       </c>
       <c r="B15" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>136391139</v>
       </c>
       <c r="B16" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>136391147</v>
       </c>
       <c r="B17" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>136391158</v>
       </c>
       <c r="B18" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>136391189</v>
       </c>
       <c r="B19" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136418441</v>
       </c>
       <c r="B20" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>136418448</v>
       </c>
       <c r="B21" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>136418460</v>
       </c>
       <c r="B22" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>136352733</v>
       </c>
       <c r="B23" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>136369839</v>
       </c>
       <c r="B24" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>136370426</v>
       </c>
       <c r="B25" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>136352753</v>
       </c>
       <c r="B26" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>136370107</v>
       </c>
       <c r="B27" t="n">
-        <v>106362</v>
+        <v>106367</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>136369811</v>
       </c>
       <c r="B28" t="n">
-        <v>79074</v>
+        <v>79076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>136369816</v>
       </c>
       <c r="B29" t="n">
-        <v>79151</v>
+        <v>79153</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>136369808</v>
       </c>
       <c r="B30" t="n">
-        <v>79158</v>
+        <v>79160</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 35174-2026 artfynd.xlsx
+++ b/artfynd/A 35174-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136370044</v>
       </c>
       <c r="B2" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>136418477</v>
       </c>
       <c r="B3" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>136418555</v>
       </c>
       <c r="B4" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>136370107</v>
       </c>
       <c r="B27" t="n">
-        <v>106367</v>
+        <v>106369</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 35174-2026 artfynd.xlsx
+++ b/artfynd/A 35174-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ30"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4124,64 +4124,56 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136352753</v>
+        <v>136885879</v>
       </c>
       <c r="B26" t="n">
-        <v>57195</v>
+        <v>58008</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Hällsjön, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>521128</v>
+        <v>521197</v>
       </c>
       <c r="R26" t="n">
-        <v>6637213</v>
+        <v>6637298</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4205,17 +4197,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>spillning på grov tallåga</t>
+          <t>Ringhack på flera granar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4226,36 +4218,31 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Per Ahlqvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Per Ahlqvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136352753</t>
+          <t>https://artportalen.se/Sighting/136885879</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136370107</v>
+        <v>136352753</v>
       </c>
       <c r="B27" t="n">
-        <v>106369</v>
+        <v>57195</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4263,42 +4250,50 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221154</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsstjärna</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lysimachia europaea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) U. Manns &amp; Anderb.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521195</v>
+        <v>521128</v>
       </c>
       <c r="R27" t="n">
-        <v>6637298</v>
+        <v>6637213</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4333,13 +4328,17 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>spillning på grov tallåga</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4362,16 +4361,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136370107</t>
+          <t>https://artportalen.se/Sighting/136352753</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136369811</v>
+        <v>136370107</v>
       </c>
       <c r="B28" t="n">
-        <v>79076</v>
+        <v>106369</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4379,37 +4378,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228595</v>
+        <v>221154</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulvit renlav</t>
+          <t>Skogsstjärna</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia arbuscula</t>
+          <t>Lysimachia europaea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Wallr.) Flot.</t>
+          <t>(L.) U. Manns &amp; Anderb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521218</v>
+        <v>521195</v>
       </c>
       <c r="R28" t="n">
-        <v>6637248</v>
+        <v>6637298</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4473,16 +4477,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136369811</t>
+          <t>https://artportalen.se/Sighting/136370107</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136369816</v>
+        <v>136369811</v>
       </c>
       <c r="B29" t="n">
-        <v>79153</v>
+        <v>79076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4490,21 +4494,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228654</v>
+        <v>228595</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grå renlav</t>
+          <t>Gulvit renlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia rangiferina</t>
+          <t>Cladonia arbuscula</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) F.H.Wigg.</t>
+          <t>(Wallr.) Flot.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4584,16 +4588,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136369816</t>
+          <t>https://artportalen.se/Sighting/136369811</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136369808</v>
+        <v>136369816</v>
       </c>
       <c r="B30" t="n">
-        <v>79160</v>
+        <v>79153</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4601,21 +4605,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228659</v>
+        <v>228654</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fönsterlav</t>
+          <t>Grå renlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia stellaris</t>
+          <t>Cladonia rangiferina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Opiz) Pouzar &amp; Vezda</t>
+          <t>(L.) F.H.Wigg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4694,6 +4698,117 @@
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136369816</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136369808</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79160</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>228659</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Fönsterlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Cladonia stellaris</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>521218</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6637248</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136369808</t>
         </is>
@@ -4730,6 +4845,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35174-2026 artfynd.xlsx
+++ b/artfynd/A 35174-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ31"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3680,32 +3680,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136352733</v>
+        <v>136940461</v>
       </c>
       <c r="B23" t="n">
-        <v>58005</v>
+        <v>79476</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3713,28 +3713,23 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kloten - Kalven/Kvarnmosen, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521191</v>
+        <v>521197</v>
       </c>
       <c r="R23" t="n">
-        <v>6637198</v>
+        <v>6637484</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3761,17 +3756,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färska hackmärken i tallåga</t>
+          <t>På underröjd gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3780,80 +3775,61 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136352733</t>
+          <t>https://artportalen.se/Sighting/136940461</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136369839</v>
+        <v>136940462</v>
       </c>
       <c r="B24" t="n">
-        <v>58005</v>
+        <v>79476</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3861,31 +3837,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kloten - Kalven/Kvarnmosen, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>521218</v>
+        <v>521170</v>
       </c>
       <c r="R24" t="n">
-        <v>6637248</v>
+        <v>6637283</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3909,17 +3878,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>hackmärken i talltorraka</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3933,75 +3897,55 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # torraka # Pinus sylvestris</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136369839</t>
+          <t>https://artportalen.se/Sighting/136940462</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136370426</v>
+        <v>136940469</v>
       </c>
       <c r="B25" t="n">
-        <v>58005</v>
+        <v>79476</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -4009,28 +3953,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kloten - Kalven/Kvarnmosen, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>521173</v>
+        <v>521243</v>
       </c>
       <c r="R25" t="n">
-        <v>6637338</v>
+        <v>6637351</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -4057,17 +3994,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>hackmärken i basen av grov granhögstubbe</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4081,70 +4013,50 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136370426</t>
+          <t>https://artportalen.se/Sighting/136940469</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136885879</v>
+        <v>136352733</v>
       </c>
       <c r="B26" t="n">
-        <v>58008</v>
+        <v>58005</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -4152,28 +4064,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hällsjön, Vstm</t>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>521197</v>
+        <v>521191</v>
       </c>
       <c r="R26" t="n">
-        <v>6637298</v>
+        <v>6637198</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4197,17 +4117,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på flera granar</t>
+          <t>Färska hackmärken i tallåga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4218,31 +4138,56 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136885879</t>
+          <t>https://artportalen.se/Sighting/136352733</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136352753</v>
+        <v>136369839</v>
       </c>
       <c r="B27" t="n">
-        <v>57195</v>
+        <v>58005</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4250,21 +4195,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -4276,7 +4221,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4290,13 +4235,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521128</v>
+        <v>521218</v>
       </c>
       <c r="R27" t="n">
-        <v>6637213</v>
+        <v>6637248</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4330,7 +4275,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>spillning på grov tallåga</t>
+          <t>hackmärken i talltorraka</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4345,6 +4290,26 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # torraka # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4361,16 +4326,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136352753</t>
+          <t>https://artportalen.se/Sighting/136369839</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136370107</v>
+        <v>136370426</v>
       </c>
       <c r="B28" t="n">
-        <v>106369</v>
+        <v>58005</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4378,42 +4343,50 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221154</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsstjärna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lysimachia europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) U. Manns &amp; Anderb.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521195</v>
+        <v>521173</v>
       </c>
       <c r="R28" t="n">
-        <v>6637298</v>
+        <v>6637338</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4448,19 +4421,43 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>hackmärken i basen av grov granhögstubbe</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4477,57 +4474,62 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136370107</t>
+          <t>https://artportalen.se/Sighting/136370426</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136369811</v>
+        <v>136885879</v>
       </c>
       <c r="B29" t="n">
-        <v>79076</v>
+        <v>58008</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228595</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gulvit renlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia arbuscula</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Wallr.) Flot.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Hällsjön, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521218</v>
+        <v>521197</v>
       </c>
       <c r="R29" t="n">
-        <v>6637248</v>
+        <v>6637298</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4551,12 +4553,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på flera granar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4565,77 +4572,73 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Per Ahlqvist</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Per Ahlqvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136369811</t>
+          <t>https://artportalen.se/Sighting/136885879</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136369816</v>
+        <v>136940463</v>
       </c>
       <c r="B30" t="n">
-        <v>79153</v>
+        <v>58008</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228654</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grå renlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia rangiferina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) F.H.Wigg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kloten - Kalven/Kvarnmosen, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521218</v>
+        <v>521221</v>
       </c>
       <c r="R30" t="n">
-        <v>6637248</v>
+        <v>6637195</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4662,12 +4665,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4676,39 +4679,38 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136369816</t>
+          <t>https://artportalen.se/Sighting/136940463</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136369808</v>
+        <v>136352753</v>
       </c>
       <c r="B31" t="n">
-        <v>79160</v>
+        <v>57195</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4716,37 +4718,50 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228659</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fönsterlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia stellaris</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Opiz) Pouzar &amp; Vezda</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521218</v>
+        <v>521128</v>
       </c>
       <c r="R31" t="n">
-        <v>6637248</v>
+        <v>6637213</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4781,13 +4796,17 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>spillning på grov tallåga</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4809,6 +4828,455 @@
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136352753</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136370107</v>
+      </c>
+      <c r="B32" t="n">
+        <v>106369</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221154</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Skogsstjärna</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lysimachia europaea</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>521195</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6637298</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136370107</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136369811</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79076</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>228595</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Gulvit renlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Cladonia arbuscula</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Wallr.) Flot.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>521218</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6637248</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136369811</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136369816</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79153</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>228654</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Grå renlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Cladonia rangiferina</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>521218</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6637248</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136369816</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136369808</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79160</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>228659</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Fönsterlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Cladonia stellaris</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>521218</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6637248</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136369808</t>
         </is>
@@ -4846,6 +5314,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35174-2026 artfynd.xlsx
+++ b/artfynd/A 35174-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ35"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4036,32 +4036,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136352733</v>
+        <v>137007756</v>
       </c>
       <c r="B26" t="n">
-        <v>58005</v>
+        <v>79476</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -4069,31 +4069,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kloten, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>521191</v>
+        <v>521199</v>
       </c>
       <c r="R26" t="n">
-        <v>6637198</v>
+        <v>6637421</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4117,17 +4105,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska hackmärken i tallåga</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4138,78 +4136,53 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136352733</t>
+          <t>https://artportalen.se/Sighting/137007756</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136369839</v>
+        <v>137007757</v>
       </c>
       <c r="B27" t="n">
-        <v>58005</v>
+        <v>79476</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -4217,31 +4190,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kloten, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521218</v>
+        <v>521180</v>
       </c>
       <c r="R27" t="n">
-        <v>6637248</v>
+        <v>6637273</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4265,17 +4226,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>hackmärken i talltorraka</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4286,53 +4257,28 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # torraka # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136369839</t>
+          <t>https://artportalen.se/Sighting/137007757</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136370426</v>
+        <v>136352733</v>
       </c>
       <c r="B28" t="n">
         <v>58005</v>
@@ -4379,14 +4325,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521173</v>
+        <v>521191</v>
       </c>
       <c r="R28" t="n">
-        <v>6637338</v>
+        <v>6637198</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4423,7 +4369,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>hackmärken i basen av grov granhögstubbe</t>
+          <t>Färska hackmärken i tallåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4442,22 +4388,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4474,33 +4420,33 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136370426</t>
+          <t>https://artportalen.se/Sighting/136352733</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136885879</v>
+        <v>136369839</v>
       </c>
       <c r="B29" t="n">
-        <v>58008</v>
+        <v>58005</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4508,28 +4454,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hällsjön, Vstm</t>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521197</v>
+        <v>521218</v>
       </c>
       <c r="R29" t="n">
-        <v>6637298</v>
+        <v>6637248</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4553,17 +4507,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på flera granar</t>
+          <t>hackmärken i talltorraka</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4574,48 +4528,73 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # torraka # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136885879</t>
+          <t>https://artportalen.se/Sighting/136369839</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136940463</v>
+        <v>136370426</v>
       </c>
       <c r="B30" t="n">
-        <v>58008</v>
+        <v>58005</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4623,22 +4602,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kloten - Kalven/Kvarnmosen, Vstm</t>
+          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521221</v>
+        <v>521173</v>
       </c>
       <c r="R30" t="n">
-        <v>6637195</v>
+        <v>6637338</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4665,12 +4655,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>hackmärken i basen av grov granhögstubbe</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4684,87 +4679,99 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136940463</t>
+          <t>https://artportalen.se/Sighting/136370426</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136352753</v>
+        <v>136885879</v>
       </c>
       <c r="B31" t="n">
-        <v>57195</v>
+        <v>58008</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Hällsjön, Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521128</v>
+        <v>521197</v>
       </c>
       <c r="R31" t="n">
-        <v>6637213</v>
+        <v>6637298</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4788,17 +4795,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>spillning på grov tallåga</t>
+          <t>Ringhack på flera granar</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4809,79 +4816,71 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Per Ahlqvist</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Per Ahlqvist</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136352753</t>
+          <t>https://artportalen.se/Sighting/136885879</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136370107</v>
+        <v>136940463</v>
       </c>
       <c r="B32" t="n">
-        <v>106369</v>
+        <v>58008</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221154</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogsstjärna</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lysimachia europaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) U. Manns &amp; Anderb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kloten - Kalven/Kvarnmosen, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521195</v>
+        <v>521221</v>
       </c>
       <c r="R32" t="n">
-        <v>6637298</v>
+        <v>6637195</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4908,12 +4907,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4922,77 +4921,77 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136370107</t>
+          <t>https://artportalen.se/Sighting/136940463</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136369811</v>
+        <v>137007621</v>
       </c>
       <c r="B33" t="n">
-        <v>79076</v>
+        <v>58008</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228595</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gulvit renlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia arbuscula</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Wallr.) Flot.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kloten, Vstm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>521218</v>
+        <v>521184</v>
       </c>
       <c r="R33" t="n">
-        <v>6637248</v>
+        <v>6637268</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -5019,12 +5018,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5033,80 +5047,75 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136369811</t>
+          <t>https://artportalen.se/Sighting/137007621</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136369816</v>
+        <v>137007622</v>
       </c>
       <c r="B34" t="n">
-        <v>79153</v>
+        <v>58008</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228654</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grå renlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia rangiferina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>Kloten, Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>521218</v>
+        <v>521225</v>
       </c>
       <c r="R34" t="n">
-        <v>6637248</v>
+        <v>6637195</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5130,12 +5139,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5144,39 +5168,33 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136369816</t>
+          <t>https://artportalen.se/Sighting/137007622</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136369808</v>
+        <v>136352753</v>
       </c>
       <c r="B35" t="n">
-        <v>79160</v>
+        <v>57195</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5184,37 +5202,50 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228659</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fönsterlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia stellaris</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Opiz) Pouzar &amp; Vezda</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521218</v>
+        <v>521128</v>
       </c>
       <c r="R35" t="n">
-        <v>6637248</v>
+        <v>6637213</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5249,13 +5280,17 @@
           <t>2026-09-04</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>spillning på grov tallåga</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5277,6 +5312,455 @@
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136352753</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136370107</v>
+      </c>
+      <c r="B36" t="n">
+        <v>106369</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221154</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Skogsstjärna</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lysimachia europaea</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kalven 500 m SV om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>521195</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6637298</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136370107</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136369811</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79076</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>228595</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Gulvit renlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Cladonia arbuscula</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Wallr.) Flot.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>521218</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6637248</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136369811</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>136369816</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79153</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>228654</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Grå renlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Cladonia rangiferina</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>521218</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6637248</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136369816</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>136369808</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79160</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>228659</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Fönsterlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Cladonia stellaris</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Sandån, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>521218</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6637248</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136369808</t>
         </is>
@@ -5318,6 +5802,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35174-2026 artfynd.xlsx
+++ b/artfynd/A 35174-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136370044</v>
       </c>
       <c r="B2" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>136418477</v>
       </c>
       <c r="B3" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>136418555</v>
       </c>
       <c r="B4" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136370093</v>
       </c>
       <c r="B5" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>136390346</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>136390391</v>
       </c>
       <c r="B7" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>136390547</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>136390574</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>136390613</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>136390682</v>
       </c>
       <c r="B11" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>136391062</v>
       </c>
       <c r="B12" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>136391089</v>
       </c>
       <c r="B13" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>136391098</v>
       </c>
       <c r="B14" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>136391109</v>
       </c>
       <c r="B15" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>136391139</v>
       </c>
       <c r="B16" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>136391147</v>
       </c>
       <c r="B17" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>136391158</v>
       </c>
       <c r="B18" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>136391189</v>
       </c>
       <c r="B19" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136418441</v>
       </c>
       <c r="B20" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>136418448</v>
       </c>
       <c r="B21" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>136418460</v>
       </c>
       <c r="B22" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>136940461</v>
       </c>
       <c r="B23" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>136940462</v>
       </c>
       <c r="B24" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>136940469</v>
       </c>
       <c r="B25" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>137007756</v>
       </c>
       <c r="B26" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>137007757</v>
       </c>
       <c r="B27" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>136370107</v>
       </c>
       <c r="B36" t="n">
-        <v>106369</v>
+        <v>106375</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>136369811</v>
       </c>
       <c r="B37" t="n">
-        <v>79076</v>
+        <v>79080</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>136369816</v>
       </c>
       <c r="B38" t="n">
-        <v>79153</v>
+        <v>79157</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>136369808</v>
       </c>
       <c r="B39" t="n">
-        <v>79160</v>
+        <v>79164</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 35174-2026 artfynd.xlsx
+++ b/artfynd/A 35174-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136370044</v>
       </c>
       <c r="B2" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>136418477</v>
       </c>
       <c r="B3" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>136418555</v>
       </c>
       <c r="B4" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136370093</v>
       </c>
       <c r="B5" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>136390346</v>
       </c>
       <c r="B6" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>136390391</v>
       </c>
       <c r="B7" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>136390547</v>
       </c>
       <c r="B8" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>136390574</v>
       </c>
       <c r="B9" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>136390613</v>
       </c>
       <c r="B10" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>136390682</v>
       </c>
       <c r="B11" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>136391062</v>
       </c>
       <c r="B12" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>136391089</v>
       </c>
       <c r="B13" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>136391098</v>
       </c>
       <c r="B14" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>136391109</v>
       </c>
       <c r="B15" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>136391139</v>
       </c>
       <c r="B16" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>136391147</v>
       </c>
       <c r="B17" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>136391158</v>
       </c>
       <c r="B18" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>136391189</v>
       </c>
       <c r="B19" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136418441</v>
       </c>
       <c r="B20" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>136418448</v>
       </c>
       <c r="B21" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>136418460</v>
       </c>
       <c r="B22" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>136940461</v>
       </c>
       <c r="B23" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>136940462</v>
       </c>
       <c r="B24" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>136940469</v>
       </c>
       <c r="B25" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>137007756</v>
       </c>
       <c r="B26" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>137007757</v>
       </c>
       <c r="B27" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>136370107</v>
       </c>
       <c r="B36" t="n">
-        <v>106375</v>
+        <v>106377</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>136369811</v>
       </c>
       <c r="B37" t="n">
-        <v>79080</v>
+        <v>79082</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>136369816</v>
       </c>
       <c r="B38" t="n">
-        <v>79157</v>
+        <v>79159</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>136369808</v>
       </c>
       <c r="B39" t="n">
-        <v>79164</v>
+        <v>79166</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 35174-2026 artfynd.xlsx
+++ b/artfynd/A 35174-2026 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>136418477</v>
       </c>
       <c r="B3" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>136418555</v>
       </c>
       <c r="B4" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136418441</v>
       </c>
       <c r="B20" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>136418448</v>
       </c>
       <c r="B21" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>136418460</v>
       </c>
       <c r="B22" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>136940461</v>
       </c>
       <c r="B23" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>136940462</v>
       </c>
       <c r="B24" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>136940469</v>
       </c>
       <c r="B25" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>137007756</v>
       </c>
       <c r="B26" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>137007757</v>
       </c>
       <c r="B27" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 35174-2026 artfynd.xlsx
+++ b/artfynd/A 35174-2026 artfynd.xlsx
@@ -3683,7 +3683,7 @@
         <v>136940461</v>
       </c>
       <c r="B23" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>136940462</v>
       </c>
       <c r="B24" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>136940469</v>
       </c>
       <c r="B25" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>137007756</v>
       </c>
       <c r="B26" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>137007757</v>
       </c>
       <c r="B27" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 35174-2026 artfynd.xlsx
+++ b/artfynd/A 35174-2026 artfynd.xlsx
@@ -3683,7 +3683,7 @@
         <v>136940461</v>
       </c>
       <c r="B23" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>136940462</v>
       </c>
       <c r="B24" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>136940469</v>
       </c>
       <c r="B25" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>137007756</v>
       </c>
       <c r="B26" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>137007757</v>
       </c>
       <c r="B27" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 35174-2026 artfynd.xlsx
+++ b/artfynd/A 35174-2026 artfynd.xlsx
@@ -3683,7 +3683,7 @@
         <v>136940461</v>
       </c>
       <c r="B23" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>136940462</v>
       </c>
       <c r="B24" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>136940469</v>
       </c>
       <c r="B25" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>137007756</v>
       </c>
       <c r="B26" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>137007757</v>
       </c>
       <c r="B27" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>136885879</v>
       </c>
       <c r="B31" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>136940463</v>
       </c>
       <c r="B32" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>137007621</v>
       </c>
       <c r="B33" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>137007622</v>
       </c>
       <c r="B34" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 35174-2026 artfynd.xlsx
+++ b/artfynd/A 35174-2026 artfynd.xlsx
@@ -3683,7 +3683,7 @@
         <v>136940461</v>
       </c>
       <c r="B23" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>136940462</v>
       </c>
       <c r="B24" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>136940469</v>
       </c>
       <c r="B25" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>137007756</v>
       </c>
       <c r="B26" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>137007757</v>
       </c>
       <c r="B27" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>136885879</v>
       </c>
       <c r="B31" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>136940463</v>
       </c>
       <c r="B32" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>137007621</v>
       </c>
       <c r="B33" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>137007622</v>
       </c>
       <c r="B34" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
